--- a/data/trans_orig/P16A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26609</t>
+          <t>27384</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50307</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>50859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83979</t>
+          <t>82054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>642687</t>
+          <t>641903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>666385</t>
+          <t>665610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649586</t>
+          <t>648697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669142</t>
+          <t>668708</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1297366</t>
+          <t>1299291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1331088</t>
+          <t>1330486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59517</t>
+          <t>57923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93710</t>
+          <t>95088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44103</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75002</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112860</t>
+          <t>109694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159455</t>
+          <t>156652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>868090</t>
+          <t>866712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>902283</t>
+          <t>903877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>893391</t>
+          <t>891559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>924290</t>
+          <t>923406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1770738</t>
+          <t>1773541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1817333</t>
+          <t>1820499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74046</t>
+          <t>74839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112880</t>
+          <t>111244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614642</t>
+          <t>614061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643638</t>
+          <t>643343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625585</t>
+          <t>624333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650661</t>
+          <t>650485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249470</t>
+          <t>1251106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288304</t>
+          <t>1287511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53142</t>
+          <t>54547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84159</t>
+          <t>83925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69673</t>
+          <t>70230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103927</t>
+          <t>105883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132045</t>
+          <t>131387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177233</t>
+          <t>180893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>858063</t>
+          <t>858297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>889080</t>
+          <t>887675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>934685</t>
+          <t>932729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>968939</t>
+          <t>968382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1803601</t>
+          <t>1799941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1848789</t>
+          <t>1849447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>198803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>255794</t>
+          <t>256265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187296</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>248215</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>405507</t>
+          <t>400407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>490355</t>
+          <t>487562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3019731</t>
+          <t>3019260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3078544</t>
+          <t>3076722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3130982</t>
+          <t>3131638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3191901</t>
+          <t>3189959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6164367</t>
+          <t>6167160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6249215</t>
+          <t>6254315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>55853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88945</t>
+          <t>88819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>45416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76676</t>
+          <t>76301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107540</t>
+          <t>108869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153101</t>
+          <t>152626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>611819</t>
+          <t>611945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>645489</t>
+          <t>644911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616675</t>
+          <t>617050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647426</t>
+          <t>647935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1241014</t>
+          <t>1241489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1286575</t>
+          <t>1285246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58465</t>
+          <t>59081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93496</t>
+          <t>93293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62353</t>
+          <t>61803</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>96461</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129030</t>
+          <t>131415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177790</t>
+          <t>179959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924451</t>
+          <t>924654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>959482</t>
+          <t>958866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928994</t>
+          <t>930189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>964297</t>
+          <t>964847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1866807</t>
+          <t>1864638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915567</t>
+          <t>1913182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67269</t>
+          <t>66914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104027</t>
+          <t>107149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46616</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76664</t>
+          <t>77401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121039</t>
+          <t>120902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167504</t>
+          <t>167766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>652511</t>
+          <t>649389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>689269</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>699619</t>
+          <t>698882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>729667</t>
+          <t>729844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1365317</t>
+          <t>1365055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1411782</t>
+          <t>1411919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76082</t>
+          <t>76492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117753</t>
+          <t>116622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79085</t>
+          <t>77748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>116824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166206</t>
+          <t>168597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220487</t>
+          <t>222316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>826186</t>
+          <t>827317</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867857</t>
+          <t>867447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>932081</t>
+          <t>931939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>969678</t>
+          <t>971015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1772216</t>
+          <t>1770387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1826497</t>
+          <t>1824106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>289602</t>
+          <t>286616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>364737</t>
+          <t>357926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>265277</t>
+          <t>262955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>330185</t>
+          <t>336776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>568021</t>
+          <t>566712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>667252</t>
+          <t>667732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3054451</t>
+          <t>3061262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3129586</t>
+          <t>3132572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3214862</t>
+          <t>3208271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3279770</t>
+          <t>3282092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6296983</t>
+          <t>6296503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6396214</t>
+          <t>6397523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28882</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53491</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73113</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78973</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116850</t>
+          <t>117278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621309</t>
+          <t>621290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>645918</t>
+          <t>646397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599726</t>
+          <t>599860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>629363</t>
+          <t>628324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1230789</t>
+          <t>1230361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1268666</t>
+          <t>1269265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69524</t>
+          <t>69784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107505</t>
+          <t>106611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106265</t>
+          <t>105618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>146153</t>
+          <t>149462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200274</t>
+          <t>200383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>914926</t>
+          <t>915820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>952907</t>
+          <t>952647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>936648</t>
+          <t>937295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>975146</t>
+          <t>974124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1865070</t>
+          <t>1864961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1919191</t>
+          <t>1915882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>39359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67014</t>
+          <t>67902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41335</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69953</t>
+          <t>70988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86625</t>
+          <t>87074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127387</t>
+          <t>128275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692538</t>
+          <t>691650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>720998</t>
+          <t>720193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>715058</t>
+          <t>714023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>743676</t>
+          <t>743558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1417176</t>
+          <t>1416288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1457938</t>
+          <t>1457489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67568</t>
+          <t>68183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101767</t>
+          <t>103318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78359</t>
+          <t>78132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117544</t>
+          <t>116988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155583</t>
+          <t>157094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206169</t>
+          <t>206854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>835800</t>
+          <t>834249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869999</t>
+          <t>869384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>926235</t>
+          <t>926791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965420</t>
+          <t>965647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1775177</t>
+          <t>1774492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825763</t>
+          <t>1824252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230616</t>
+          <t>229355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>296394</t>
+          <t>294465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,82 +6014,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>295278</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>261307</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>330404</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>556411</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>510177</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>605538</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>295278</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>261087</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>328950</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>556411</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>508103</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>600878</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3097956</t>
+          <t>3099885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3163734</t>
+          <t>3164995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,82 +6127,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3249264</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3214138</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3283235</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6382481</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6333354</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6428715</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>91,27%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3249264</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3215592</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3283455</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6382481</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6338014</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6430789</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>51026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>54364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66054</t>
+          <t>67184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96894</t>
+          <t>97523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>585257</t>
+          <t>584415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>608820</t>
+          <t>607622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621035</t>
+          <t>621058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641964</t>
+          <t>641934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1213969</t>
+          <t>1213340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1244809</t>
+          <t>1243679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>32729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103219</t>
+          <t>101489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72253</t>
+          <t>71050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104632</t>
+          <t>103396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108225</t>
+          <t>103161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193139</t>
+          <t>188967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1089645</t>
+          <t>1091375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1157816</t>
+          <t>1160135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>853474</t>
+          <t>854710</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>885853</t>
+          <t>887056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1957832</t>
+          <t>1962004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2042746</t>
+          <t>2047810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63218</t>
+          <t>64021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58824</t>
+          <t>61344</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56467</t>
+          <t>54720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108879</t>
+          <t>111305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640466</t>
+          <t>639663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671154</t>
+          <t>669783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>873195</t>
+          <t>870675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>912051</t>
+          <t>913259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1526824</t>
+          <t>1524398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1579236</t>
+          <t>1580983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56884</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95084</t>
+          <t>94218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70723</t>
+          <t>70125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109096</t>
+          <t>107395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137159</t>
+          <t>137980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190836</t>
+          <t>193129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831747</t>
+          <t>832613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869947</t>
+          <t>872050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>982278</t>
+          <t>983979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1020651</t>
+          <t>1021249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1827369</t>
+          <t>1825076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1881046</t>
+          <t>1880225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174870</t>
+          <t>175822</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265333</t>
+          <t>267910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>211773</t>
+          <t>214202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>296798</t>
+          <t>295894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>428685</t>
+          <t>424323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>549704</t>
+          <t>548369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3193487</t>
+          <t>3190910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3283950</t>
+          <t>3282998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3360123</t>
+          <t>3361027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3445148</t>
+          <t>3442719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6566037</t>
+          <t>6567372</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6687056</t>
+          <t>6691418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>26747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51091</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>40735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50859</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82054</t>
+          <t>80815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641903</t>
+          <t>640971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665610</t>
+          <t>666247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>648697</t>
+          <t>647616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668708</t>
+          <t>669011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1299291</t>
+          <t>1300530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1330486</t>
+          <t>1330447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57923</t>
+          <t>58969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95088</t>
+          <t>93775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>76069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109694</t>
+          <t>112431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156652</t>
+          <t>157274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>866712</t>
+          <t>868025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>903877</t>
+          <t>902831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>891559</t>
+          <t>892324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>923406</t>
+          <t>923776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1773541</t>
+          <t>1772919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1820499</t>
+          <t>1817762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64448</t>
+          <t>64090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33356</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>56953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74839</t>
+          <t>76158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111244</t>
+          <t>113777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614061</t>
+          <t>614419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643343</t>
+          <t>642944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624333</t>
+          <t>626888</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650485</t>
+          <t>651570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251106</t>
+          <t>1248573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287511</t>
+          <t>1286192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54547</t>
+          <t>54944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83925</t>
+          <t>84763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70230</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105883</t>
+          <t>103853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131387</t>
+          <t>131259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180893</t>
+          <t>179276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>858297</t>
+          <t>857459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>887675</t>
+          <t>887278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>932729</t>
+          <t>934759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>968382</t>
+          <t>969914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1799941</t>
+          <t>1801558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1849447</t>
+          <t>1849575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198803</t>
+          <t>200192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>258625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>189238</t>
+          <t>190866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247559</t>
+          <t>247570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400407</t>
+          <t>405828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>487562</t>
+          <t>486224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3019260</t>
+          <t>3016900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3076722</t>
+          <t>3075333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3131638</t>
+          <t>3131627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3189959</t>
+          <t>3188331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6167160</t>
+          <t>6168498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6254315</t>
+          <t>6248894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55853</t>
+          <t>55050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88819</t>
+          <t>87027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45416</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76301</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>107605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152626</t>
+          <t>151256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>611945</t>
+          <t>613737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>644911</t>
+          <t>645714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>617050</t>
+          <t>617891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647935</t>
+          <t>645905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1241489</t>
+          <t>1242859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1285246</t>
+          <t>1286510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>57621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>94236</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61803</t>
+          <t>62570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96461</t>
+          <t>97534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131415</t>
+          <t>130944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179959</t>
+          <t>180447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924654</t>
+          <t>923711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>958866</t>
+          <t>960326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>930189</t>
+          <t>929116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>964847</t>
+          <t>964080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1864638</t>
+          <t>1864150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1913182</t>
+          <t>1913653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66914</t>
+          <t>67329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107149</t>
+          <t>104421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>46319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77401</t>
+          <t>76289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120902</t>
+          <t>120161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167766</t>
+          <t>167980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>649389</t>
+          <t>652117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>689624</t>
+          <t>689209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698882</t>
+          <t>699994</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>729844</t>
+          <t>729964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1365055</t>
+          <t>1364841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1411919</t>
+          <t>1412660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76492</t>
+          <t>77316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116622</t>
+          <t>117332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77748</t>
+          <t>77889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116824</t>
+          <t>115424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168597</t>
+          <t>165919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222316</t>
+          <t>221138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>827317</t>
+          <t>826607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867447</t>
+          <t>866623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>931939</t>
+          <t>933339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>971015</t>
+          <t>970874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1770387</t>
+          <t>1771565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1824106</t>
+          <t>1826784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>286616</t>
+          <t>286621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>357926</t>
+          <t>359400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>262955</t>
+          <t>258865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>336776</t>
+          <t>330169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>566712</t>
+          <t>569144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>667732</t>
+          <t>671198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3061262</t>
+          <t>3059788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3132572</t>
+          <t>3132567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3208271</t>
+          <t>3214878</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3282092</t>
+          <t>3286182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6296503</t>
+          <t>6293037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6397523</t>
+          <t>6395091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53510</t>
+          <t>53708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72979</t>
+          <t>72667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78374</t>
+          <t>79894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117278</t>
+          <t>117222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621290</t>
+          <t>621092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>646397</t>
+          <t>646189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599860</t>
+          <t>600172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>628324</t>
+          <t>629460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1230361</t>
+          <t>1230417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1269265</t>
+          <t>1267745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69784</t>
+          <t>68834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106611</t>
+          <t>106135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68789</t>
+          <t>69371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105618</t>
+          <t>105302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149462</t>
+          <t>149428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200383</t>
+          <t>202718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>915820</t>
+          <t>916296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>952647</t>
+          <t>953597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>937295</t>
+          <t>937611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>974124</t>
+          <t>973542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1864961</t>
+          <t>1862626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915882</t>
+          <t>1915916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41453</t>
+          <t>40866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70988</t>
+          <t>70855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87074</t>
+          <t>86100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128275</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>691650</t>
+          <t>693214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>720193</t>
+          <t>721263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>714023</t>
+          <t>714156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>743558</t>
+          <t>744145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1416288</t>
+          <t>1417167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1457489</t>
+          <t>1458463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68183</t>
+          <t>65818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103318</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78132</t>
+          <t>76916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116988</t>
+          <t>117022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157094</t>
+          <t>155290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206854</t>
+          <t>207581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>834249</t>
+          <t>837415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869384</t>
+          <t>871749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>926791</t>
+          <t>926757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965647</t>
+          <t>966863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1774492</t>
+          <t>1773765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1824252</t>
+          <t>1826056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229355</t>
+          <t>231227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>294465</t>
+          <t>294228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261307</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>330404</t>
+          <t>330691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>510177</t>
+          <t>513221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>605538</t>
+          <t>608988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3099885</t>
+          <t>3100122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3164995</t>
+          <t>3163123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3214138</t>
+          <t>3213851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3283235</t>
+          <t>3282238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6333354</t>
+          <t>6329904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6428715</t>
+          <t>6425671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -6569,27 +6569,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37584</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>29890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>55452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>47102</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>36653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>57940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>80771</t>
+          <t>87812</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67184</t>
+          <t>73579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97523</t>
+          <t>106036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -6682,22 +6682,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>597857</t>
+          <t>650000</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>584415</t>
+          <t>635258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607622</t>
+          <t>660820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>632235</t>
+          <t>685680</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621058</t>
+          <t>674842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641934</t>
+          <t>696129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1230092</t>
+          <t>1335680</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1213340</t>
+          <t>1317456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1243679</t>
+          <t>1349913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310863</t>
+          <t>1423492</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310863</t>
+          <t>1423492</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310863</t>
+          <t>1423492</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72922</t>
+          <t>80082</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32729</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101489</t>
+          <t>101618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>92017</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71050</t>
+          <t>75279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103396</t>
+          <t>110648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>158666</t>
+          <t>172098</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103161</t>
+          <t>147878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188967</t>
+          <t>202879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1119942</t>
+          <t>968835</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1091375</t>
+          <t>947299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1160135</t>
+          <t>988965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>872362</t>
+          <t>978821</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>854710</t>
+          <t>960190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>887056</t>
+          <t>995559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1992305</t>
+          <t>1947657</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1962004</t>
+          <t>1916876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2047810</t>
+          <t>1971877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45646</t>
+          <t>51171</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33901</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64021</t>
+          <t>70235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41946</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61344</t>
+          <t>65322</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>87592</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54720</t>
+          <t>82376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111305</t>
+          <t>125264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>658038</t>
+          <t>750915</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639663</t>
+          <t>731851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669783</t>
+          <t>763626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>890073</t>
+          <t>759975</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>870675</t>
+          <t>745575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>913259</t>
+          <t>772515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1548111</t>
+          <t>1510890</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1524398</t>
+          <t>1487719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1580983</t>
+          <t>1530607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932019</t>
+          <t>810897</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932019</t>
+          <t>810897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932019</t>
+          <t>810897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635703</t>
+          <t>1612983</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635703</t>
+          <t>1612983</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635703</t>
+          <t>1612983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72479</t>
+          <t>81707</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54781</t>
+          <t>63734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>104478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90615</t>
+          <t>98282</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70125</t>
+          <t>83179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107395</t>
+          <t>115461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>163094</t>
+          <t>179989</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137980</t>
+          <t>156064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193129</t>
+          <t>205503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>854352</t>
+          <t>908355</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>832613</t>
+          <t>885584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872050</t>
+          <t>926328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1000759</t>
+          <t>1018749</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>983979</t>
+          <t>1001570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1021249</t>
+          <t>1033852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1855111</t>
+          <t>1927104</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1825076</t>
+          <t>1901590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1880225</t>
+          <t>1951029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175822</t>
+          <t>221574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>267910</t>
+          <t>293991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>261492</t>
+          <t>288323</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>214202</t>
+          <t>260374</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295894</t>
+          <t>318892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>490123</t>
+          <t>541992</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>424323</t>
+          <t>500101</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>548369</t>
+          <t>589879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3230189</t>
+          <t>3278106</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3190910</t>
+          <t>3237784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3282998</t>
+          <t>3310201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3395429</t>
+          <t>3443225</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3361027</t>
+          <t>3412656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3442719</t>
+          <t>3471174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6625618</t>
+          <t>6721331</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6567372</t>
+          <t>6673444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6691418</t>
+          <t>6763222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>93,11%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
